--- a/src/assets/worklog/07.VD.xlsx
+++ b/src/assets/worklog/07.VD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\eurocell-mes-be\data\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\eurocell-mes-be\src\assets\worklog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6DFB1A6-0301-4FD9-BF5F-9A28F91F0128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6441A38-D677-4B48-9478-F1353372C44C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-17100" yWindow="390" windowWidth="19140" windowHeight="15210" xr2:uid="{5727D201-909C-4737-94BB-43A538AD22EF}"/>
+    <workbookView xWindow="1590" yWindow="300" windowWidth="26040" windowHeight="15045" xr2:uid="{5727D201-909C-4737-94BB-43A538AD22EF}"/>
   </bookViews>
   <sheets>
     <sheet name="원본" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
     <definedName name="lowerTimerTime">원본!$L$39</definedName>
     <definedName name="manufactureDate">원본!$C$7</definedName>
     <definedName name="plant">원본!$G$9</definedName>
-    <definedName name="productionId">원본!$G$7</definedName>
+    <definedName name="projectId">원본!$G$7</definedName>
     <definedName name="remark">원본!$A$47</definedName>
     <definedName name="reviewer">원본!$K$5</definedName>
     <definedName name="safety">원본!$K$44</definedName>
@@ -600,12 +600,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -615,66 +609,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -702,7 +636,73 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1051,17 +1051,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
       <c r="J1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1073,596 +1073,596 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="7"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
+      <c r="A2" s="41"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
+      <c r="A3" s="41"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
+      <c r="A4" s="41"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="40"/>
+      <c r="L4" s="40"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
+      <c r="A5" s="41"/>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="11"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="9"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="12" t="s">
+      <c r="B7" s="38"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="12"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="12" t="s">
+      <c r="F7" s="38"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="12"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="40"/>
+      <c r="L7" s="40"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
+      <c r="A8" s="38"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="38"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="40"/>
+      <c r="L8" s="40"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="12" t="s">
+      <c r="B9" s="38"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="12"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="12" t="s">
+      <c r="F9" s="38"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="12"/>
-      <c r="K9" s="8" t="s">
+      <c r="J9" s="38"/>
+      <c r="K9" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="L9" s="8"/>
+      <c r="L9" s="40"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="12"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
+      <c r="A10" s="38"/>
+      <c r="B10" s="38"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="40"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="11"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="9"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="13" t="s">
+      <c r="B12" s="38"/>
+      <c r="C12" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13" t="s">
+      <c r="D12" s="39"/>
+      <c r="E12" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13" t="s">
+      <c r="F12" s="39"/>
+      <c r="G12" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13" t="s">
+      <c r="H12" s="39"/>
+      <c r="I12" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13" t="s">
+      <c r="J12" s="39"/>
+      <c r="K12" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="L12" s="13"/>
+      <c r="L12" s="39"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="13"/>
+      <c r="A13" s="38"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="39"/>
+      <c r="L13" s="39"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="14"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="14"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="19"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="14"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="31"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="31"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="31"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="11"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="9"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="12"/>
-      <c r="C19" s="13" t="s">
+      <c r="B19" s="38"/>
+      <c r="C19" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13" t="s">
+      <c r="D19" s="39"/>
+      <c r="E19" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13" t="s">
+      <c r="F19" s="39"/>
+      <c r="G19" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13" t="s">
+      <c r="H19" s="39"/>
+      <c r="I19" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13" t="s">
+      <c r="J19" s="39"/>
+      <c r="K19" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="L19" s="13"/>
+      <c r="L19" s="39"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
-      <c r="L20" s="13"/>
+      <c r="A20" s="38"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
+      <c r="K20" s="39"/>
+      <c r="L20" s="39"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="14"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="14"/>
-      <c r="L21" s="14"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="19"/>
     </row>
     <row r="22" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="14"/>
-      <c r="L22" s="14"/>
+      <c r="A22" s="19"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="19"/>
+      <c r="L22" s="19"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="14"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="14"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16"/>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
+      <c r="A24" s="19"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="31"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="31"/>
+      <c r="K24" s="31"/>
+      <c r="L24" s="31"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="31"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="31"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="14"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16"/>
-      <c r="J26" s="16"/>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
+      <c r="A26" s="19"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="14" t="s">
+      <c r="A27" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B27" s="14"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="16"/>
-      <c r="J27" s="16"/>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="31"/>
+      <c r="I27" s="31"/>
+      <c r="J27" s="31"/>
+      <c r="K27" s="31"/>
+      <c r="L27" s="31"/>
     </row>
     <row r="28" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="21"/>
-      <c r="B28" s="21"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="23"/>
-      <c r="J28" s="23"/>
-      <c r="K28" s="23"/>
-      <c r="L28" s="23"/>
+      <c r="A28" s="35"/>
+      <c r="B28" s="35"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="37"/>
+      <c r="H28" s="37"/>
+      <c r="I28" s="37"/>
+      <c r="J28" s="37"/>
+      <c r="K28" s="37"/>
+      <c r="L28" s="37"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="18" t="s">
+      <c r="A29" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="18"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="18"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
-      <c r="K29" s="18"/>
-      <c r="L29" s="18"/>
+      <c r="B29" s="32"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="34"/>
+      <c r="J29" s="34"/>
+      <c r="K29" s="32"/>
+      <c r="L29" s="32"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="14"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="17"/>
-      <c r="J30" s="17"/>
-      <c r="K30" s="14"/>
-      <c r="L30" s="14"/>
+      <c r="A30" s="19"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="14" t="s">
+      <c r="A31" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B31" s="14"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="16"/>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="31"/>
+      <c r="H31" s="31"/>
+      <c r="I31" s="31"/>
+      <c r="J31" s="31"/>
+      <c r="K31" s="31"/>
+      <c r="L31" s="31"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="14"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="16"/>
-      <c r="I32" s="16"/>
-      <c r="J32" s="16"/>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
+      <c r="A32" s="19"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="31"/>
+      <c r="I32" s="31"/>
+      <c r="J32" s="31"/>
+      <c r="K32" s="31"/>
+      <c r="L32" s="31"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" s="14" t="s">
+      <c r="A33" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B33" s="14"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="16"/>
-      <c r="H33" s="16"/>
-      <c r="I33" s="16"/>
-      <c r="J33" s="16"/>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="31"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="31"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="14"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="16"/>
-      <c r="H34" s="16"/>
-      <c r="I34" s="16"/>
-      <c r="J34" s="16"/>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
+      <c r="A34" s="19"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="30"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="31"/>
+      <c r="H34" s="31"/>
+      <c r="I34" s="31"/>
+      <c r="J34" s="31"/>
+      <c r="K34" s="31"/>
+      <c r="L34" s="31"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="14" t="s">
+      <c r="A35" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B35" s="14"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="16"/>
-      <c r="H35" s="16"/>
-      <c r="I35" s="16"/>
-      <c r="J35" s="16"/>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="31"/>
+      <c r="H35" s="31"/>
+      <c r="I35" s="31"/>
+      <c r="J35" s="31"/>
+      <c r="K35" s="31"/>
+      <c r="L35" s="31"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="14"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="15"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="16"/>
-      <c r="H36" s="16"/>
-      <c r="I36" s="16"/>
-      <c r="J36" s="16"/>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
+      <c r="A36" s="19"/>
+      <c r="B36" s="19"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="30"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="19"/>
+      <c r="G36" s="31"/>
+      <c r="H36" s="31"/>
+      <c r="I36" s="31"/>
+      <c r="J36" s="31"/>
+      <c r="K36" s="31"/>
+      <c r="L36" s="31"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A37" s="9" t="s">
+      <c r="A37" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="10"/>
-      <c r="J37" s="10"/>
-      <c r="K37" s="10"/>
-      <c r="L37" s="11"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
+      <c r="I37" s="8"/>
+      <c r="J37" s="8"/>
+      <c r="K37" s="8"/>
+      <c r="L37" s="9"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A38" s="24" t="s">
+      <c r="A38" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="B38" s="25"/>
-      <c r="C38" s="24"/>
-      <c r="D38" s="25"/>
-      <c r="E38" s="28" t="s">
+      <c r="B38" s="23"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="F38" s="29"/>
+      <c r="F38" s="27"/>
       <c r="G38" s="2" t="s">
         <v>42</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="I38" s="28" t="s">
+      <c r="I38" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="J38" s="29"/>
+      <c r="J38" s="27"/>
       <c r="K38" s="2" t="s">
         <v>42</v>
       </c>
@@ -1671,245 +1671,342 @@
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A39" s="26"/>
-      <c r="B39" s="27"/>
-      <c r="C39" s="26"/>
-      <c r="D39" s="27"/>
-      <c r="E39" s="30"/>
-      <c r="F39" s="31"/>
+      <c r="A39" s="24"/>
+      <c r="B39" s="25"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="28"/>
+      <c r="F39" s="29"/>
       <c r="G39" s="4"/>
       <c r="H39" s="5"/>
-      <c r="I39" s="30"/>
-      <c r="J39" s="31"/>
+      <c r="I39" s="28"/>
+      <c r="J39" s="29"/>
       <c r="K39" s="4"/>
       <c r="L39" s="5"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A40" s="9" t="s">
+      <c r="A40" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B40" s="10"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="10"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
-      <c r="I40" s="10"/>
-      <c r="J40" s="10"/>
-      <c r="K40" s="10"/>
-      <c r="L40" s="11"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="8"/>
+      <c r="K40" s="8"/>
+      <c r="L40" s="9"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A41" s="14" t="s">
+      <c r="A41" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="B41" s="14"/>
-      <c r="C41" s="41" t="s">
+      <c r="B41" s="19"/>
+      <c r="C41" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="D41" s="17"/>
-      <c r="E41" s="14" t="s">
+      <c r="D41" s="20"/>
+      <c r="E41" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="F41" s="14"/>
-      <c r="G41" s="17"/>
-      <c r="H41" s="17"/>
-      <c r="I41" s="14" t="s">
+      <c r="F41" s="19"/>
+      <c r="G41" s="20"/>
+      <c r="H41" s="20"/>
+      <c r="I41" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="J41" s="14"/>
-      <c r="K41" s="41" t="s">
+      <c r="J41" s="19"/>
+      <c r="K41" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="L41" s="17"/>
+      <c r="L41" s="20"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A42" s="14"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="17"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="17"/>
-      <c r="H42" s="17"/>
-      <c r="I42" s="14"/>
-      <c r="J42" s="14"/>
-      <c r="K42" s="17"/>
-      <c r="L42" s="17"/>
+      <c r="A42" s="19"/>
+      <c r="B42" s="19"/>
+      <c r="C42" s="20"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="19"/>
+      <c r="F42" s="19"/>
+      <c r="G42" s="20"/>
+      <c r="H42" s="20"/>
+      <c r="I42" s="19"/>
+      <c r="J42" s="19"/>
+      <c r="K42" s="20"/>
+      <c r="L42" s="20"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="9" t="s">
+      <c r="A43" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B43" s="10"/>
-      <c r="C43" s="10"/>
-      <c r="D43" s="10"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
-      <c r="I43" s="10"/>
-      <c r="J43" s="10"/>
-      <c r="K43" s="10"/>
-      <c r="L43" s="11"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="8"/>
+      <c r="I43" s="8"/>
+      <c r="J43" s="8"/>
+      <c r="K43" s="8"/>
+      <c r="L43" s="9"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A44" s="14" t="s">
+      <c r="A44" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B44" s="14"/>
-      <c r="C44" s="17" t="s">
+      <c r="B44" s="19"/>
+      <c r="C44" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="D44" s="17"/>
-      <c r="E44" s="14" t="s">
+      <c r="D44" s="20"/>
+      <c r="E44" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="F44" s="14"/>
-      <c r="G44" s="17" t="s">
+      <c r="F44" s="19"/>
+      <c r="G44" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="H44" s="17"/>
-      <c r="I44" s="14" t="s">
+      <c r="H44" s="20"/>
+      <c r="I44" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="J44" s="14"/>
-      <c r="K44" s="17" t="s">
+      <c r="J44" s="19"/>
+      <c r="K44" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="L44" s="17"/>
+      <c r="L44" s="20"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A45" s="14"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="17"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="17"/>
-      <c r="H45" s="17"/>
-      <c r="I45" s="14"/>
-      <c r="J45" s="14"/>
-      <c r="K45" s="17"/>
-      <c r="L45" s="17"/>
+      <c r="A45" s="19"/>
+      <c r="B45" s="19"/>
+      <c r="C45" s="20"/>
+      <c r="D45" s="20"/>
+      <c r="E45" s="19"/>
+      <c r="F45" s="19"/>
+      <c r="G45" s="20"/>
+      <c r="H45" s="20"/>
+      <c r="I45" s="19"/>
+      <c r="J45" s="19"/>
+      <c r="K45" s="20"/>
+      <c r="L45" s="20"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A46" s="9" t="s">
+      <c r="A46" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B46" s="10"/>
-      <c r="C46" s="10"/>
-      <c r="D46" s="10"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="10"/>
-      <c r="G46" s="10"/>
-      <c r="H46" s="10"/>
-      <c r="I46" s="10"/>
-      <c r="J46" s="10"/>
-      <c r="K46" s="10"/>
-      <c r="L46" s="11"/>
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="8"/>
+      <c r="I46" s="8"/>
+      <c r="J46" s="8"/>
+      <c r="K46" s="8"/>
+      <c r="L46" s="9"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A47" s="32"/>
-      <c r="B47" s="33"/>
-      <c r="C47" s="33"/>
-      <c r="D47" s="33"/>
-      <c r="E47" s="33"/>
-      <c r="F47" s="33"/>
-      <c r="G47" s="33"/>
-      <c r="H47" s="33"/>
-      <c r="I47" s="33"/>
-      <c r="J47" s="33"/>
-      <c r="K47" s="33"/>
-      <c r="L47" s="34"/>
+      <c r="A47" s="10"/>
+      <c r="B47" s="11"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="11"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="11"/>
+      <c r="I47" s="11"/>
+      <c r="J47" s="11"/>
+      <c r="K47" s="11"/>
+      <c r="L47" s="12"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A48" s="35"/>
-      <c r="B48" s="36"/>
-      <c r="C48" s="36"/>
-      <c r="D48" s="36"/>
-      <c r="E48" s="36"/>
-      <c r="F48" s="36"/>
-      <c r="G48" s="36"/>
-      <c r="H48" s="36"/>
-      <c r="I48" s="36"/>
-      <c r="J48" s="36"/>
-      <c r="K48" s="36"/>
-      <c r="L48" s="37"/>
+      <c r="A48" s="13"/>
+      <c r="B48" s="14"/>
+      <c r="C48" s="14"/>
+      <c r="D48" s="14"/>
+      <c r="E48" s="14"/>
+      <c r="F48" s="14"/>
+      <c r="G48" s="14"/>
+      <c r="H48" s="14"/>
+      <c r="I48" s="14"/>
+      <c r="J48" s="14"/>
+      <c r="K48" s="14"/>
+      <c r="L48" s="15"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A49" s="35"/>
-      <c r="B49" s="36"/>
-      <c r="C49" s="36"/>
-      <c r="D49" s="36"/>
-      <c r="E49" s="36"/>
-      <c r="F49" s="36"/>
-      <c r="G49" s="36"/>
-      <c r="H49" s="36"/>
-      <c r="I49" s="36"/>
-      <c r="J49" s="36"/>
-      <c r="K49" s="36"/>
-      <c r="L49" s="37"/>
+      <c r="A49" s="13"/>
+      <c r="B49" s="14"/>
+      <c r="C49" s="14"/>
+      <c r="D49" s="14"/>
+      <c r="E49" s="14"/>
+      <c r="F49" s="14"/>
+      <c r="G49" s="14"/>
+      <c r="H49" s="14"/>
+      <c r="I49" s="14"/>
+      <c r="J49" s="14"/>
+      <c r="K49" s="14"/>
+      <c r="L49" s="15"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A50" s="35"/>
-      <c r="B50" s="36"/>
-      <c r="C50" s="36"/>
-      <c r="D50" s="36"/>
-      <c r="E50" s="36"/>
-      <c r="F50" s="36"/>
-      <c r="G50" s="36"/>
-      <c r="H50" s="36"/>
-      <c r="I50" s="36"/>
-      <c r="J50" s="36"/>
-      <c r="K50" s="36"/>
-      <c r="L50" s="37"/>
+      <c r="A50" s="13"/>
+      <c r="B50" s="14"/>
+      <c r="C50" s="14"/>
+      <c r="D50" s="14"/>
+      <c r="E50" s="14"/>
+      <c r="F50" s="14"/>
+      <c r="G50" s="14"/>
+      <c r="H50" s="14"/>
+      <c r="I50" s="14"/>
+      <c r="J50" s="14"/>
+      <c r="K50" s="14"/>
+      <c r="L50" s="15"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A51" s="35"/>
-      <c r="B51" s="36"/>
-      <c r="C51" s="36"/>
-      <c r="D51" s="36"/>
-      <c r="E51" s="36"/>
-      <c r="F51" s="36"/>
-      <c r="G51" s="36"/>
-      <c r="H51" s="36"/>
-      <c r="I51" s="36"/>
-      <c r="J51" s="36"/>
-      <c r="K51" s="36"/>
-      <c r="L51" s="37"/>
+      <c r="A51" s="13"/>
+      <c r="B51" s="14"/>
+      <c r="C51" s="14"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="14"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="14"/>
+      <c r="H51" s="14"/>
+      <c r="I51" s="14"/>
+      <c r="J51" s="14"/>
+      <c r="K51" s="14"/>
+      <c r="L51" s="15"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A52" s="35"/>
-      <c r="B52" s="36"/>
-      <c r="C52" s="36"/>
-      <c r="D52" s="36"/>
-      <c r="E52" s="36"/>
-      <c r="F52" s="36"/>
-      <c r="G52" s="36"/>
-      <c r="H52" s="36"/>
-      <c r="I52" s="36"/>
-      <c r="J52" s="36"/>
-      <c r="K52" s="36"/>
-      <c r="L52" s="37"/>
+      <c r="A52" s="13"/>
+      <c r="B52" s="14"/>
+      <c r="C52" s="14"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="14"/>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14"/>
+      <c r="H52" s="14"/>
+      <c r="I52" s="14"/>
+      <c r="J52" s="14"/>
+      <c r="K52" s="14"/>
+      <c r="L52" s="15"/>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A53" s="38"/>
-      <c r="B53" s="39"/>
-      <c r="C53" s="39"/>
-      <c r="D53" s="39"/>
-      <c r="E53" s="39"/>
-      <c r="F53" s="39"/>
-      <c r="G53" s="39"/>
-      <c r="H53" s="39"/>
-      <c r="I53" s="39"/>
-      <c r="J53" s="39"/>
-      <c r="K53" s="39"/>
-      <c r="L53" s="40"/>
+      <c r="A53" s="16"/>
+      <c r="B53" s="17"/>
+      <c r="C53" s="17"/>
+      <c r="D53" s="17"/>
+      <c r="E53" s="17"/>
+      <c r="F53" s="17"/>
+      <c r="G53" s="17"/>
+      <c r="H53" s="17"/>
+      <c r="I53" s="17"/>
+      <c r="J53" s="17"/>
+      <c r="K53" s="17"/>
+      <c r="L53" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="112">
+    <mergeCell ref="A1:I5"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="L2:L4"/>
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A7:B8"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="E7:F8"/>
+    <mergeCell ref="G7:H8"/>
+    <mergeCell ref="I7:J8"/>
+    <mergeCell ref="A11:L11"/>
+    <mergeCell ref="A12:B13"/>
+    <mergeCell ref="C12:D13"/>
+    <mergeCell ref="E12:F13"/>
+    <mergeCell ref="G12:H13"/>
+    <mergeCell ref="I12:J13"/>
+    <mergeCell ref="K12:L13"/>
+    <mergeCell ref="K7:L8"/>
+    <mergeCell ref="A9:B10"/>
+    <mergeCell ref="C9:D10"/>
+    <mergeCell ref="E9:F10"/>
+    <mergeCell ref="G9:H10"/>
+    <mergeCell ref="I9:J10"/>
+    <mergeCell ref="K9:L10"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E16:F17"/>
+    <mergeCell ref="G16:H17"/>
+    <mergeCell ref="I16:J17"/>
+    <mergeCell ref="K16:L17"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="C14:D15"/>
+    <mergeCell ref="E14:F15"/>
+    <mergeCell ref="G14:H15"/>
+    <mergeCell ref="I14:J15"/>
+    <mergeCell ref="K14:L15"/>
+    <mergeCell ref="A21:B22"/>
+    <mergeCell ref="C21:D22"/>
+    <mergeCell ref="E21:F22"/>
+    <mergeCell ref="G21:H22"/>
+    <mergeCell ref="I21:J22"/>
+    <mergeCell ref="K21:L22"/>
+    <mergeCell ref="A18:L18"/>
+    <mergeCell ref="A19:B20"/>
+    <mergeCell ref="C19:D20"/>
+    <mergeCell ref="E19:F20"/>
+    <mergeCell ref="G19:H20"/>
+    <mergeCell ref="I19:J20"/>
+    <mergeCell ref="K19:L20"/>
+    <mergeCell ref="A25:B26"/>
+    <mergeCell ref="C25:D26"/>
+    <mergeCell ref="E25:F26"/>
+    <mergeCell ref="G25:H26"/>
+    <mergeCell ref="I25:J26"/>
+    <mergeCell ref="K25:L26"/>
+    <mergeCell ref="A23:B24"/>
+    <mergeCell ref="C23:D24"/>
+    <mergeCell ref="E23:F24"/>
+    <mergeCell ref="G23:H24"/>
+    <mergeCell ref="I23:J24"/>
+    <mergeCell ref="K23:L24"/>
+    <mergeCell ref="A29:B30"/>
+    <mergeCell ref="C29:D30"/>
+    <mergeCell ref="E29:F30"/>
+    <mergeCell ref="G29:H30"/>
+    <mergeCell ref="I29:J30"/>
+    <mergeCell ref="K29:L30"/>
+    <mergeCell ref="A27:B28"/>
+    <mergeCell ref="C27:D28"/>
+    <mergeCell ref="E27:F28"/>
+    <mergeCell ref="G27:H28"/>
+    <mergeCell ref="I27:J28"/>
+    <mergeCell ref="K27:L28"/>
+    <mergeCell ref="A33:B34"/>
+    <mergeCell ref="C33:D34"/>
+    <mergeCell ref="E33:F34"/>
+    <mergeCell ref="G33:H34"/>
+    <mergeCell ref="I33:J34"/>
+    <mergeCell ref="K33:L34"/>
+    <mergeCell ref="A31:B32"/>
+    <mergeCell ref="C31:D32"/>
+    <mergeCell ref="E31:F32"/>
+    <mergeCell ref="G31:H32"/>
+    <mergeCell ref="I31:J32"/>
+    <mergeCell ref="K31:L32"/>
+    <mergeCell ref="A37:L37"/>
+    <mergeCell ref="A38:B39"/>
+    <mergeCell ref="C38:D39"/>
+    <mergeCell ref="E38:F39"/>
+    <mergeCell ref="I38:J39"/>
+    <mergeCell ref="A40:L40"/>
+    <mergeCell ref="A35:B36"/>
+    <mergeCell ref="C35:D36"/>
+    <mergeCell ref="E35:F36"/>
+    <mergeCell ref="G35:H36"/>
+    <mergeCell ref="I35:J36"/>
+    <mergeCell ref="K35:L36"/>
     <mergeCell ref="A46:L46"/>
     <mergeCell ref="A47:L53"/>
     <mergeCell ref="A44:B45"/>
@@ -1925,103 +2022,6 @@
     <mergeCell ref="I41:J42"/>
     <mergeCell ref="K41:L42"/>
     <mergeCell ref="A43:L43"/>
-    <mergeCell ref="A37:L37"/>
-    <mergeCell ref="A38:B39"/>
-    <mergeCell ref="C38:D39"/>
-    <mergeCell ref="E38:F39"/>
-    <mergeCell ref="I38:J39"/>
-    <mergeCell ref="A40:L40"/>
-    <mergeCell ref="A35:B36"/>
-    <mergeCell ref="C35:D36"/>
-    <mergeCell ref="E35:F36"/>
-    <mergeCell ref="G35:H36"/>
-    <mergeCell ref="I35:J36"/>
-    <mergeCell ref="K35:L36"/>
-    <mergeCell ref="A33:B34"/>
-    <mergeCell ref="C33:D34"/>
-    <mergeCell ref="E33:F34"/>
-    <mergeCell ref="G33:H34"/>
-    <mergeCell ref="I33:J34"/>
-    <mergeCell ref="K33:L34"/>
-    <mergeCell ref="A31:B32"/>
-    <mergeCell ref="C31:D32"/>
-    <mergeCell ref="E31:F32"/>
-    <mergeCell ref="G31:H32"/>
-    <mergeCell ref="I31:J32"/>
-    <mergeCell ref="K31:L32"/>
-    <mergeCell ref="A29:B30"/>
-    <mergeCell ref="C29:D30"/>
-    <mergeCell ref="E29:F30"/>
-    <mergeCell ref="G29:H30"/>
-    <mergeCell ref="I29:J30"/>
-    <mergeCell ref="K29:L30"/>
-    <mergeCell ref="A27:B28"/>
-    <mergeCell ref="C27:D28"/>
-    <mergeCell ref="E27:F28"/>
-    <mergeCell ref="G27:H28"/>
-    <mergeCell ref="I27:J28"/>
-    <mergeCell ref="K27:L28"/>
-    <mergeCell ref="A25:B26"/>
-    <mergeCell ref="C25:D26"/>
-    <mergeCell ref="E25:F26"/>
-    <mergeCell ref="G25:H26"/>
-    <mergeCell ref="I25:J26"/>
-    <mergeCell ref="K25:L26"/>
-    <mergeCell ref="A23:B24"/>
-    <mergeCell ref="C23:D24"/>
-    <mergeCell ref="E23:F24"/>
-    <mergeCell ref="G23:H24"/>
-    <mergeCell ref="I23:J24"/>
-    <mergeCell ref="K23:L24"/>
-    <mergeCell ref="A21:B22"/>
-    <mergeCell ref="C21:D22"/>
-    <mergeCell ref="E21:F22"/>
-    <mergeCell ref="G21:H22"/>
-    <mergeCell ref="I21:J22"/>
-    <mergeCell ref="K21:L22"/>
-    <mergeCell ref="A18:L18"/>
-    <mergeCell ref="A19:B20"/>
-    <mergeCell ref="C19:D20"/>
-    <mergeCell ref="E19:F20"/>
-    <mergeCell ref="G19:H20"/>
-    <mergeCell ref="I19:J20"/>
-    <mergeCell ref="K19:L20"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E16:F17"/>
-    <mergeCell ref="G16:H17"/>
-    <mergeCell ref="I16:J17"/>
-    <mergeCell ref="K16:L17"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:D15"/>
-    <mergeCell ref="E14:F15"/>
-    <mergeCell ref="G14:H15"/>
-    <mergeCell ref="I14:J15"/>
-    <mergeCell ref="K14:L15"/>
-    <mergeCell ref="A11:L11"/>
-    <mergeCell ref="A12:B13"/>
-    <mergeCell ref="C12:D13"/>
-    <mergeCell ref="E12:F13"/>
-    <mergeCell ref="G12:H13"/>
-    <mergeCell ref="I12:J13"/>
-    <mergeCell ref="K12:L13"/>
-    <mergeCell ref="K7:L8"/>
-    <mergeCell ref="A9:B10"/>
-    <mergeCell ref="C9:D10"/>
-    <mergeCell ref="E9:F10"/>
-    <mergeCell ref="G9:H10"/>
-    <mergeCell ref="I9:J10"/>
-    <mergeCell ref="K9:L10"/>
-    <mergeCell ref="A1:I5"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="K2:K4"/>
-    <mergeCell ref="L2:L4"/>
-    <mergeCell ref="A6:L6"/>
-    <mergeCell ref="A7:B8"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="E7:F8"/>
-    <mergeCell ref="G7:H8"/>
-    <mergeCell ref="I7:J8"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/assets/worklog/07.VD.xlsx
+++ b/src/assets/worklog/07.VD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\eurocell-mes-be\src\assets\worklog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2792EFEB-8BC8-4514-8A15-A681359E7BD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DBE1AD7-CEB2-46FB-BAB0-D9B4BABB8F86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-13110" yWindow="165" windowWidth="22830" windowHeight="15045" xr2:uid="{5727D201-909C-4737-94BB-43A538AD22EF}"/>
+    <workbookView xWindow="2145" yWindow="165" windowWidth="25260" windowHeight="15135" xr2:uid="{5727D201-909C-4737-94BB-43A538AD22EF}"/>
   </bookViews>
   <sheets>
     <sheet name="원본" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <definedName name="equipmentLowerNumber">원본!$H$44</definedName>
     <definedName name="equipmentUpperNumber">원본!$G$44</definedName>
     <definedName name="line">원본!$C$9</definedName>
+    <definedName name="lowerElectrode">원본!$B$17</definedName>
     <definedName name="lowerInputOutputTime">원본!$D$37</definedName>
     <definedName name="lowerInputQuantity1">원본!$D$31</definedName>
     <definedName name="lowerInputQuantity2">원본!$G$31</definedName>
@@ -77,6 +78,7 @@
     <definedName name="safety">원본!$K$46</definedName>
     <definedName name="shift">원본!$K$9</definedName>
     <definedName name="tempHumi">원본!$C$46</definedName>
+    <definedName name="upperElectrode">원본!$B$14</definedName>
     <definedName name="upperInputOutputTime">원본!$D$29</definedName>
     <definedName name="upperInputQuantity1">원본!$D$23</definedName>
     <definedName name="upperInputQuantity2">원본!$G$23</definedName>
@@ -147,7 +149,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="54">
   <si>
     <t>진공 건조 작업 일지</t>
   </si>
@@ -232,10 +234,6 @@
   </si>
   <si>
     <t>상부</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>음극</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
@@ -628,23 +626,200 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -667,185 +842,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1182,7 +1180,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="662" row="4">
+  <wetp:taskpane dockstate="right" visibility="0" width="705" row="4">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -1215,362 +1213,358 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="3" t="s">
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="74"/>
+      <c r="J1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
+      <c r="A2" s="74"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="74"/>
+      <c r="I2" s="74"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="66"/>
     </row>
     <row r="3" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
+      <c r="A3" s="74"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="66"/>
+      <c r="K3" s="66"/>
+      <c r="L3" s="66"/>
     </row>
     <row r="4" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
+      <c r="A4" s="74"/>
+      <c r="B4" s="74"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="66"/>
+      <c r="K4" s="66"/>
+      <c r="L4" s="66"/>
     </row>
     <row r="5" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3" t="s">
+      <c r="A5" s="74"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="L5" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="7"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="16"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="8" t="s">
+      <c r="B7" s="67"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="67" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="8"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="8" t="s">
+      <c r="F7" s="67"/>
+      <c r="G7" s="66"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="J7" s="8"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
+      <c r="J7" s="67"/>
+      <c r="K7" s="66"/>
+      <c r="L7" s="66"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
+      <c r="A8" s="67"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="67"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="67"/>
+      <c r="J8" s="67"/>
+      <c r="K8" s="66"/>
+      <c r="L8" s="66"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="8" t="s">
+      <c r="B9" s="67"/>
+      <c r="C9" s="66"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="8"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="8" t="s">
+      <c r="F9" s="67"/>
+      <c r="G9" s="66"/>
+      <c r="H9" s="66"/>
+      <c r="I9" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="J9" s="8"/>
-      <c r="K9" s="4" t="s">
+      <c r="J9" s="67"/>
+      <c r="K9" s="66" t="s">
         <v>13</v>
       </c>
-      <c r="L9" s="4"/>
+      <c r="L9" s="66"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
+      <c r="A10" s="67"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="66"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="67"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="66"/>
+      <c r="H10" s="66"/>
+      <c r="I10" s="67"/>
+      <c r="J10" s="67"/>
+      <c r="K10" s="66"/>
+      <c r="L10" s="66"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="7"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="16"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11" t="s">
+      <c r="B12" s="69"/>
+      <c r="C12" s="69"/>
+      <c r="D12" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="E12" s="12"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="11" t="s">
+      <c r="E12" s="71"/>
+      <c r="F12" s="72"/>
+      <c r="G12" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="H12" s="12"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="9" t="s">
+      <c r="H12" s="71"/>
+      <c r="I12" s="72"/>
+      <c r="J12" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="K12" s="10"/>
-      <c r="L12" s="14"/>
+      <c r="K12" s="69"/>
+      <c r="L12" s="73"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="13"/>
-      <c r="F13" s="17" t="s">
+      <c r="E13" s="72"/>
+      <c r="F13" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="H13" s="13"/>
-      <c r="I13" s="17" t="s">
+      <c r="H13" s="72"/>
+      <c r="I13" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="J13" s="11" t="s">
+      <c r="J13" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="K13" s="13"/>
-      <c r="L13" s="17" t="s">
+      <c r="K13" s="72"/>
+      <c r="L13" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="60"/>
+      <c r="C14" s="7">
+        <v>1</v>
+      </c>
+      <c r="D14" s="63"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="63"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="63"/>
+      <c r="K14" s="64"/>
+      <c r="L14" s="8"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="35"/>
+      <c r="B15" s="61"/>
+      <c r="C15" s="7">
+        <v>2</v>
+      </c>
+      <c r="D15" s="63"/>
+      <c r="E15" s="64"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="63"/>
+      <c r="H15" s="64"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="63"/>
+      <c r="K15" s="64"/>
+      <c r="L15" s="8"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="19"/>
+      <c r="B16" s="62"/>
+      <c r="C16" s="7">
+        <v>3</v>
+      </c>
+      <c r="D16" s="63"/>
+      <c r="E16" s="64"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="63"/>
+      <c r="H16" s="64"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="63"/>
+      <c r="K16" s="64"/>
+      <c r="L16" s="8"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="20">
+      <c r="B17" s="60"/>
+      <c r="C17" s="7">
         <v>1</v>
       </c>
-      <c r="D14" s="21"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="23"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="22"/>
-      <c r="L14" s="23"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="24"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="20">
+      <c r="D17" s="63"/>
+      <c r="E17" s="64"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="63"/>
+      <c r="H17" s="64"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="63"/>
+      <c r="K17" s="65"/>
+      <c r="L17" s="8"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="35"/>
+      <c r="B18" s="61"/>
+      <c r="C18" s="7">
         <v>2</v>
       </c>
-      <c r="D15" s="21"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="23"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="22"/>
-      <c r="L15" s="23"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="26"/>
-      <c r="B16" s="27"/>
-      <c r="C16" s="20">
+      <c r="D18" s="63"/>
+      <c r="E18" s="64"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="63"/>
+      <c r="H18" s="64"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="63"/>
+      <c r="K18" s="64"/>
+      <c r="L18" s="8"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="19"/>
+      <c r="B19" s="62"/>
+      <c r="C19" s="7">
         <v>3</v>
       </c>
-      <c r="D16" s="21"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="23"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="22"/>
-      <c r="L16" s="23"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="18" t="s">
+      <c r="D19" s="63"/>
+      <c r="E19" s="64"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="63"/>
+      <c r="H19" s="64"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="63"/>
+      <c r="K19" s="64"/>
+      <c r="L19" s="8"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="20">
-        <v>1</v>
-      </c>
-      <c r="D17" s="21"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="23"/>
-      <c r="J17" s="21"/>
-      <c r="K17" s="28"/>
-      <c r="L17" s="23"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="24"/>
-      <c r="B18" s="25"/>
-      <c r="C18" s="20">
-        <v>2</v>
-      </c>
-      <c r="D18" s="21"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="23"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="22"/>
-      <c r="L18" s="23"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="26"/>
-      <c r="B19" s="27"/>
-      <c r="C19" s="20">
-        <v>3</v>
-      </c>
-      <c r="D19" s="21"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="23"/>
-      <c r="J19" s="21"/>
-      <c r="K19" s="22"/>
-      <c r="L19" s="23"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="7"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="16"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="29" t="s">
@@ -1609,13 +1603,13 @@
       <c r="L22" s="34"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="24" t="s">
+      <c r="A23" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="C23" s="35"/>
+      <c r="B23" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="18"/>
       <c r="D23" s="36"/>
       <c r="E23" s="37"/>
       <c r="F23" s="38"/>
@@ -1627,121 +1621,121 @@
       <c r="L23" s="38"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="24"/>
-      <c r="B24" s="26"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="42"/>
-      <c r="G24" s="40"/>
-      <c r="H24" s="41"/>
-      <c r="I24" s="42"/>
-      <c r="J24" s="40"/>
-      <c r="K24" s="41"/>
-      <c r="L24" s="42"/>
+      <c r="A24" s="35"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="41"/>
+      <c r="J24" s="39"/>
+      <c r="K24" s="40"/>
+      <c r="L24" s="41"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="24"/>
-      <c r="B25" s="18" t="s">
+      <c r="A25" s="35"/>
+      <c r="B25" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="18"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="43"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="44"/>
+      <c r="J25" s="42"/>
+      <c r="K25" s="43"/>
+      <c r="L25" s="44"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="35"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="45"/>
+      <c r="H26" s="46"/>
+      <c r="I26" s="47"/>
+      <c r="J26" s="45"/>
+      <c r="K26" s="46"/>
+      <c r="L26" s="47"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="35"/>
+      <c r="B27" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="35"/>
-      <c r="D25" s="43"/>
-      <c r="E25" s="44"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="43"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="45"/>
-      <c r="J25" s="43"/>
-      <c r="K25" s="44"/>
-      <c r="L25" s="45"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="24"/>
-      <c r="B26" s="26"/>
-      <c r="C26" s="39"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="48"/>
-      <c r="G26" s="46"/>
-      <c r="H26" s="47"/>
-      <c r="I26" s="48"/>
-      <c r="J26" s="46"/>
-      <c r="K26" s="47"/>
-      <c r="L26" s="48"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="24"/>
-      <c r="B27" s="18" t="s">
+      <c r="C27" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="23" t="s">
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="35"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D27" s="49"/>
-      <c r="E27" s="49"/>
-      <c r="F27" s="49"/>
-      <c r="G27" s="49"/>
-      <c r="H27" s="49"/>
-      <c r="I27" s="49"/>
-      <c r="J27" s="49"/>
-      <c r="K27" s="49"/>
-      <c r="L27" s="49"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="24"/>
-      <c r="B28" s="26"/>
-      <c r="C28" s="23" t="s">
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="35"/>
+      <c r="B29" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D28" s="49"/>
-      <c r="E28" s="49"/>
-      <c r="F28" s="49"/>
-      <c r="G28" s="49"/>
-      <c r="H28" s="49"/>
-      <c r="I28" s="49"/>
-      <c r="J28" s="49"/>
-      <c r="K28" s="49"/>
-      <c r="L28" s="49"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="24"/>
-      <c r="B29" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="C29" s="35"/>
-      <c r="D29" s="50"/>
-      <c r="E29" s="51"/>
-      <c r="F29" s="51"/>
-      <c r="G29" s="51"/>
-      <c r="H29" s="51"/>
-      <c r="I29" s="51"/>
-      <c r="J29" s="51"/>
-      <c r="K29" s="51"/>
-      <c r="L29" s="35"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="48"/>
+      <c r="E29" s="49"/>
+      <c r="F29" s="49"/>
+      <c r="G29" s="49"/>
+      <c r="H29" s="49"/>
+      <c r="I29" s="49"/>
+      <c r="J29" s="49"/>
+      <c r="K29" s="49"/>
+      <c r="L29" s="18"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="24"/>
-      <c r="B30" s="26"/>
-      <c r="C30" s="39"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="52"/>
-      <c r="F30" s="52"/>
-      <c r="G30" s="52"/>
-      <c r="H30" s="52"/>
-      <c r="I30" s="52"/>
-      <c r="J30" s="52"/>
-      <c r="K30" s="52"/>
-      <c r="L30" s="39"/>
+      <c r="A30" s="35"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="50"/>
+      <c r="F30" s="50"/>
+      <c r="G30" s="50"/>
+      <c r="H30" s="50"/>
+      <c r="I30" s="50"/>
+      <c r="J30" s="50"/>
+      <c r="K30" s="50"/>
+      <c r="L30" s="20"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="53" t="s">
-        <v>26</v>
-      </c>
-      <c r="B31" s="53" t="s">
-        <v>28</v>
-      </c>
-      <c r="C31" s="53"/>
+      <c r="A31" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" s="28"/>
       <c r="D31" s="36"/>
       <c r="E31" s="37"/>
       <c r="F31" s="38"/>
@@ -1753,408 +1747,408 @@
       <c r="L31" s="38"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="53"/>
-      <c r="B32" s="53"/>
-      <c r="C32" s="53"/>
-      <c r="D32" s="40"/>
-      <c r="E32" s="41"/>
-      <c r="F32" s="42"/>
-      <c r="G32" s="40"/>
-      <c r="H32" s="41"/>
-      <c r="I32" s="42"/>
-      <c r="J32" s="40"/>
-      <c r="K32" s="41"/>
-      <c r="L32" s="42"/>
+      <c r="A32" s="28"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="40"/>
+      <c r="F32" s="41"/>
+      <c r="G32" s="39"/>
+      <c r="H32" s="40"/>
+      <c r="I32" s="41"/>
+      <c r="J32" s="39"/>
+      <c r="K32" s="40"/>
+      <c r="L32" s="41"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" s="53"/>
-      <c r="B33" s="18" t="s">
+      <c r="A33" s="28"/>
+      <c r="B33" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="18"/>
+      <c r="D33" s="42"/>
+      <c r="E33" s="43"/>
+      <c r="F33" s="44"/>
+      <c r="G33" s="42"/>
+      <c r="H33" s="43"/>
+      <c r="I33" s="44"/>
+      <c r="J33" s="42"/>
+      <c r="K33" s="43"/>
+      <c r="L33" s="44"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="28"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="45"/>
+      <c r="E34" s="46"/>
+      <c r="F34" s="47"/>
+      <c r="G34" s="45"/>
+      <c r="H34" s="46"/>
+      <c r="I34" s="47"/>
+      <c r="J34" s="45"/>
+      <c r="K34" s="46"/>
+      <c r="L34" s="47"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" s="28"/>
+      <c r="B35" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C33" s="35"/>
-      <c r="D33" s="43"/>
-      <c r="E33" s="44"/>
-      <c r="F33" s="45"/>
-      <c r="G33" s="43"/>
-      <c r="H33" s="44"/>
-      <c r="I33" s="45"/>
-      <c r="J33" s="43"/>
-      <c r="K33" s="44"/>
-      <c r="L33" s="45"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="53"/>
-      <c r="B34" s="26"/>
-      <c r="C34" s="39"/>
-      <c r="D34" s="46"/>
-      <c r="E34" s="47"/>
-      <c r="F34" s="48"/>
-      <c r="G34" s="46"/>
-      <c r="H34" s="47"/>
-      <c r="I34" s="48"/>
-      <c r="J34" s="46"/>
-      <c r="K34" s="47"/>
-      <c r="L34" s="48"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="53"/>
-      <c r="B35" s="18" t="s">
+      <c r="C35" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C35" s="23" t="s">
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10"/>
+      <c r="I35" s="10"/>
+      <c r="J35" s="10"/>
+      <c r="K35" s="10"/>
+      <c r="L35" s="10"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" s="28"/>
+      <c r="B36" s="19"/>
+      <c r="C36" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D35" s="49"/>
-      <c r="E35" s="49"/>
-      <c r="F35" s="49"/>
-      <c r="G35" s="49"/>
-      <c r="H35" s="49"/>
-      <c r="I35" s="49"/>
-      <c r="J35" s="49"/>
-      <c r="K35" s="49"/>
-      <c r="L35" s="49"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="53"/>
-      <c r="B36" s="26"/>
-      <c r="C36" s="23" t="s">
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10"/>
+      <c r="I36" s="10"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="10"/>
+      <c r="L36" s="10"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" s="28"/>
+      <c r="B37" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D36" s="49"/>
-      <c r="E36" s="49"/>
-      <c r="F36" s="49"/>
-      <c r="G36" s="49"/>
-      <c r="H36" s="49"/>
-      <c r="I36" s="49"/>
-      <c r="J36" s="49"/>
-      <c r="K36" s="49"/>
-      <c r="L36" s="49"/>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A37" s="53"/>
-      <c r="B37" s="18" t="s">
+      <c r="C37" s="18"/>
+      <c r="D37" s="48"/>
+      <c r="E37" s="49"/>
+      <c r="F37" s="49"/>
+      <c r="G37" s="49"/>
+      <c r="H37" s="49"/>
+      <c r="I37" s="49"/>
+      <c r="J37" s="49"/>
+      <c r="K37" s="49"/>
+      <c r="L37" s="18"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" s="28"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="50"/>
+      <c r="F38" s="50"/>
+      <c r="G38" s="50"/>
+      <c r="H38" s="50"/>
+      <c r="I38" s="50"/>
+      <c r="J38" s="50"/>
+      <c r="K38" s="50"/>
+      <c r="L38" s="20"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C37" s="35"/>
-      <c r="D37" s="50"/>
-      <c r="E37" s="51"/>
-      <c r="F37" s="51"/>
-      <c r="G37" s="51"/>
-      <c r="H37" s="51"/>
-      <c r="I37" s="51"/>
-      <c r="J37" s="51"/>
-      <c r="K37" s="51"/>
-      <c r="L37" s="35"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A38" s="53"/>
-      <c r="B38" s="26"/>
-      <c r="C38" s="39"/>
-      <c r="D38" s="26"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="52"/>
-      <c r="G38" s="52"/>
-      <c r="H38" s="52"/>
-      <c r="I38" s="52"/>
-      <c r="J38" s="52"/>
-      <c r="K38" s="52"/>
-      <c r="L38" s="39"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A39" s="54" t="s">
+      <c r="B39" s="14"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="15"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="15"/>
+      <c r="I39" s="15"/>
+      <c r="J39" s="15"/>
+      <c r="K39" s="15"/>
+      <c r="L39" s="16"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="B39" s="55"/>
-      <c r="C39" s="55"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="6"/>
-      <c r="L39" s="7"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A40" s="18" t="s">
+      <c r="B40" s="18"/>
+      <c r="C40" s="17">
+        <v>-760</v>
+      </c>
+      <c r="D40" s="18"/>
+      <c r="E40" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="B40" s="35"/>
-      <c r="C40" s="18">
-        <v>-760</v>
-      </c>
-      <c r="D40" s="35"/>
-      <c r="E40" s="56" t="s">
+      <c r="F40" s="22"/>
+      <c r="G40" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="F40" s="57"/>
-      <c r="G40" s="58" t="s">
+      <c r="H40" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="H40" s="59" t="s">
+      <c r="I40" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="I40" s="56" t="s">
+      <c r="J40" s="22"/>
+      <c r="K40" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="L40" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" s="19"/>
+      <c r="B41" s="20"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="23"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="6"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="23"/>
+      <c r="J41" s="24"/>
+      <c r="K41" s="6">
+        <v>12</v>
+      </c>
+      <c r="L41" s="9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="J40" s="57"/>
-      <c r="K40" s="58" t="s">
+      <c r="B42" s="15"/>
+      <c r="C42" s="15"/>
+      <c r="D42" s="15"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="15"/>
+      <c r="H42" s="15"/>
+      <c r="I42" s="15"/>
+      <c r="J42" s="15"/>
+      <c r="K42" s="15"/>
+      <c r="L42" s="16"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="B43" s="26"/>
+      <c r="C43" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="D43" s="28"/>
+      <c r="E43" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="F43" s="26"/>
+      <c r="G43" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="H43" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="L40" s="58" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A41" s="26"/>
-      <c r="B41" s="39"/>
-      <c r="C41" s="26"/>
-      <c r="D41" s="39"/>
-      <c r="E41" s="60"/>
-      <c r="F41" s="61"/>
-      <c r="G41" s="62"/>
-      <c r="H41" s="63"/>
-      <c r="I41" s="60"/>
-      <c r="J41" s="61"/>
-      <c r="K41" s="62">
-        <v>12</v>
-      </c>
-      <c r="L41" s="63">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A42" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6"/>
-      <c r="J42" s="6"/>
-      <c r="K42" s="6"/>
-      <c r="L42" s="7"/>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="64" t="s">
+      <c r="I43" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="J43" s="26"/>
+      <c r="K43" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="L43" s="28"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44" s="26"/>
+      <c r="B44" s="26"/>
+      <c r="C44" s="28"/>
+      <c r="D44" s="28"/>
+      <c r="E44" s="26"/>
+      <c r="F44" s="26"/>
+      <c r="G44" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I44" s="26"/>
+      <c r="J44" s="26"/>
+      <c r="K44" s="28"/>
+      <c r="L44" s="28"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A45" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="B45" s="15"/>
+      <c r="C45" s="15"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="15"/>
+      <c r="G45" s="15"/>
+      <c r="H45" s="15"/>
+      <c r="I45" s="15"/>
+      <c r="J45" s="15"/>
+      <c r="K45" s="15"/>
+      <c r="L45" s="16"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A46" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="B46" s="26"/>
+      <c r="C46" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="D46" s="28"/>
+      <c r="E46" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="F46" s="26"/>
+      <c r="G46" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="B43" s="64"/>
-      <c r="C43" s="65" t="s">
-        <v>42</v>
-      </c>
-      <c r="D43" s="53"/>
-      <c r="E43" s="64" t="s">
-        <v>43</v>
-      </c>
-      <c r="F43" s="64"/>
-      <c r="G43" s="58" t="s">
-        <v>37</v>
-      </c>
-      <c r="H43" s="59" t="s">
-        <v>38</v>
-      </c>
-      <c r="I43" s="64" t="s">
-        <v>44</v>
-      </c>
-      <c r="J43" s="64"/>
-      <c r="K43" s="65" t="s">
-        <v>45</v>
-      </c>
-      <c r="L43" s="53"/>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A44" s="64"/>
-      <c r="B44" s="64"/>
-      <c r="C44" s="53"/>
-      <c r="D44" s="53"/>
-      <c r="E44" s="64"/>
-      <c r="F44" s="64"/>
-      <c r="G44" s="62" t="s">
-        <v>46</v>
-      </c>
-      <c r="H44" s="63" t="s">
-        <v>47</v>
-      </c>
-      <c r="I44" s="64"/>
-      <c r="J44" s="64"/>
-      <c r="K44" s="53"/>
-      <c r="L44" s="53"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A45" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="6"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="6"/>
-      <c r="J45" s="6"/>
-      <c r="K45" s="6"/>
-      <c r="L45" s="7"/>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A46" s="64" t="s">
-        <v>49</v>
-      </c>
-      <c r="B46" s="64"/>
-      <c r="C46" s="53" t="s">
-        <v>50</v>
-      </c>
-      <c r="D46" s="53"/>
-      <c r="E46" s="64" t="s">
+      <c r="H46" s="28"/>
+      <c r="I46" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="F46" s="64"/>
-      <c r="G46" s="53" t="s">
-        <v>42</v>
-      </c>
-      <c r="H46" s="53"/>
-      <c r="I46" s="64" t="s">
+      <c r="J46" s="26"/>
+      <c r="K46" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="J46" s="64"/>
-      <c r="K46" s="53" t="s">
+      <c r="L46" s="28"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A47" s="26"/>
+      <c r="B47" s="26"/>
+      <c r="C47" s="28"/>
+      <c r="D47" s="28"/>
+      <c r="E47" s="26"/>
+      <c r="F47" s="26"/>
+      <c r="G47" s="28"/>
+      <c r="H47" s="28"/>
+      <c r="I47" s="26"/>
+      <c r="J47" s="26"/>
+      <c r="K47" s="28"/>
+      <c r="L47" s="28"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A48" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="L46" s="53"/>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A47" s="64"/>
-      <c r="B47" s="64"/>
-      <c r="C47" s="53"/>
-      <c r="D47" s="53"/>
-      <c r="E47" s="64"/>
-      <c r="F47" s="64"/>
-      <c r="G47" s="53"/>
-      <c r="H47" s="53"/>
-      <c r="I47" s="64"/>
-      <c r="J47" s="64"/>
-      <c r="K47" s="53"/>
-      <c r="L47" s="53"/>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A48" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B48" s="6"/>
-      <c r="C48" s="6"/>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="6"/>
-      <c r="J48" s="6"/>
-      <c r="K48" s="6"/>
-      <c r="L48" s="7"/>
+      <c r="B48" s="15"/>
+      <c r="C48" s="15"/>
+      <c r="D48" s="15"/>
+      <c r="E48" s="15"/>
+      <c r="F48" s="15"/>
+      <c r="G48" s="15"/>
+      <c r="H48" s="15"/>
+      <c r="I48" s="15"/>
+      <c r="J48" s="15"/>
+      <c r="K48" s="15"/>
+      <c r="L48" s="16"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A49" s="66"/>
-      <c r="B49" s="67"/>
-      <c r="C49" s="67"/>
-      <c r="D49" s="67"/>
-      <c r="E49" s="67"/>
-      <c r="F49" s="67"/>
-      <c r="G49" s="67"/>
-      <c r="H49" s="67"/>
-      <c r="I49" s="67"/>
-      <c r="J49" s="67"/>
-      <c r="K49" s="67"/>
-      <c r="L49" s="68"/>
+      <c r="A49" s="51"/>
+      <c r="B49" s="52"/>
+      <c r="C49" s="52"/>
+      <c r="D49" s="52"/>
+      <c r="E49" s="52"/>
+      <c r="F49" s="52"/>
+      <c r="G49" s="52"/>
+      <c r="H49" s="52"/>
+      <c r="I49" s="52"/>
+      <c r="J49" s="52"/>
+      <c r="K49" s="52"/>
+      <c r="L49" s="53"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A50" s="69"/>
-      <c r="B50" s="70"/>
-      <c r="C50" s="70"/>
-      <c r="D50" s="70"/>
-      <c r="E50" s="70"/>
-      <c r="F50" s="70"/>
-      <c r="G50" s="70"/>
-      <c r="H50" s="70"/>
-      <c r="I50" s="70"/>
-      <c r="J50" s="70"/>
-      <c r="K50" s="70"/>
-      <c r="L50" s="71"/>
+      <c r="A50" s="54"/>
+      <c r="B50" s="55"/>
+      <c r="C50" s="55"/>
+      <c r="D50" s="55"/>
+      <c r="E50" s="55"/>
+      <c r="F50" s="55"/>
+      <c r="G50" s="55"/>
+      <c r="H50" s="55"/>
+      <c r="I50" s="55"/>
+      <c r="J50" s="55"/>
+      <c r="K50" s="55"/>
+      <c r="L50" s="56"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A51" s="69"/>
-      <c r="B51" s="70"/>
-      <c r="C51" s="70"/>
-      <c r="D51" s="70"/>
-      <c r="E51" s="70"/>
-      <c r="F51" s="70"/>
-      <c r="G51" s="70"/>
-      <c r="H51" s="70"/>
-      <c r="I51" s="70"/>
-      <c r="J51" s="70"/>
-      <c r="K51" s="70"/>
-      <c r="L51" s="71"/>
+      <c r="A51" s="54"/>
+      <c r="B51" s="55"/>
+      <c r="C51" s="55"/>
+      <c r="D51" s="55"/>
+      <c r="E51" s="55"/>
+      <c r="F51" s="55"/>
+      <c r="G51" s="55"/>
+      <c r="H51" s="55"/>
+      <c r="I51" s="55"/>
+      <c r="J51" s="55"/>
+      <c r="K51" s="55"/>
+      <c r="L51" s="56"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A52" s="69"/>
-      <c r="B52" s="70"/>
-      <c r="C52" s="70"/>
-      <c r="D52" s="70"/>
-      <c r="E52" s="70"/>
-      <c r="F52" s="70"/>
-      <c r="G52" s="70"/>
-      <c r="H52" s="70"/>
-      <c r="I52" s="70"/>
-      <c r="J52" s="70"/>
-      <c r="K52" s="70"/>
-      <c r="L52" s="71"/>
+      <c r="A52" s="54"/>
+      <c r="B52" s="55"/>
+      <c r="C52" s="55"/>
+      <c r="D52" s="55"/>
+      <c r="E52" s="55"/>
+      <c r="F52" s="55"/>
+      <c r="G52" s="55"/>
+      <c r="H52" s="55"/>
+      <c r="I52" s="55"/>
+      <c r="J52" s="55"/>
+      <c r="K52" s="55"/>
+      <c r="L52" s="56"/>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A53" s="69"/>
-      <c r="B53" s="70"/>
-      <c r="C53" s="70"/>
-      <c r="D53" s="70"/>
-      <c r="E53" s="70"/>
-      <c r="F53" s="70"/>
-      <c r="G53" s="70"/>
-      <c r="H53" s="70"/>
-      <c r="I53" s="70"/>
-      <c r="J53" s="70"/>
-      <c r="K53" s="70"/>
-      <c r="L53" s="71"/>
+      <c r="A53" s="54"/>
+      <c r="B53" s="55"/>
+      <c r="C53" s="55"/>
+      <c r="D53" s="55"/>
+      <c r="E53" s="55"/>
+      <c r="F53" s="55"/>
+      <c r="G53" s="55"/>
+      <c r="H53" s="55"/>
+      <c r="I53" s="55"/>
+      <c r="J53" s="55"/>
+      <c r="K53" s="55"/>
+      <c r="L53" s="56"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A54" s="69"/>
-      <c r="B54" s="70"/>
-      <c r="C54" s="70"/>
-      <c r="D54" s="70"/>
-      <c r="E54" s="70"/>
-      <c r="F54" s="70"/>
-      <c r="G54" s="70"/>
-      <c r="H54" s="70"/>
-      <c r="I54" s="70"/>
-      <c r="J54" s="70"/>
-      <c r="K54" s="70"/>
-      <c r="L54" s="71"/>
+      <c r="A54" s="54"/>
+      <c r="B54" s="55"/>
+      <c r="C54" s="55"/>
+      <c r="D54" s="55"/>
+      <c r="E54" s="55"/>
+      <c r="F54" s="55"/>
+      <c r="G54" s="55"/>
+      <c r="H54" s="55"/>
+      <c r="I54" s="55"/>
+      <c r="J54" s="55"/>
+      <c r="K54" s="55"/>
+      <c r="L54" s="56"/>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A55" s="72"/>
-      <c r="B55" s="73"/>
-      <c r="C55" s="73"/>
-      <c r="D55" s="73"/>
-      <c r="E55" s="73"/>
-      <c r="F55" s="73"/>
-      <c r="G55" s="73"/>
-      <c r="H55" s="73"/>
-      <c r="I55" s="73"/>
-      <c r="J55" s="73"/>
-      <c r="K55" s="73"/>
-      <c r="L55" s="74"/>
+      <c r="A55" s="57"/>
+      <c r="B55" s="58"/>
+      <c r="C55" s="58"/>
+      <c r="D55" s="58"/>
+      <c r="E55" s="58"/>
+      <c r="F55" s="58"/>
+      <c r="G55" s="58"/>
+      <c r="H55" s="58"/>
+      <c r="I55" s="58"/>
+      <c r="J55" s="58"/>
+      <c r="K55" s="58"/>
+      <c r="L55" s="59"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J56"/>
@@ -2183,41 +2177,53 @@
     </row>
   </sheetData>
   <mergeCells count="96">
-    <mergeCell ref="A39:L39"/>
-    <mergeCell ref="A40:B41"/>
-    <mergeCell ref="C40:D41"/>
-    <mergeCell ref="E40:F41"/>
-    <mergeCell ref="I40:J41"/>
-    <mergeCell ref="A42:L42"/>
-    <mergeCell ref="A43:B44"/>
-    <mergeCell ref="C43:D44"/>
-    <mergeCell ref="E43:F44"/>
-    <mergeCell ref="I43:J44"/>
-    <mergeCell ref="K43:L44"/>
-    <mergeCell ref="A20:L20"/>
-    <mergeCell ref="A21:C22"/>
-    <mergeCell ref="D21:F22"/>
-    <mergeCell ref="G21:I22"/>
-    <mergeCell ref="J21:L22"/>
-    <mergeCell ref="A23:A30"/>
-    <mergeCell ref="B23:C24"/>
-    <mergeCell ref="D23:F24"/>
-    <mergeCell ref="G23:I24"/>
-    <mergeCell ref="J23:L24"/>
-    <mergeCell ref="B25:C26"/>
-    <mergeCell ref="D25:F26"/>
-    <mergeCell ref="G25:I26"/>
-    <mergeCell ref="J25:L26"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="B29:C30"/>
-    <mergeCell ref="D29:L30"/>
-    <mergeCell ref="A45:L45"/>
-    <mergeCell ref="A46:B47"/>
-    <mergeCell ref="C46:D47"/>
-    <mergeCell ref="E46:F47"/>
-    <mergeCell ref="G46:H47"/>
-    <mergeCell ref="I46:J47"/>
-    <mergeCell ref="K46:L47"/>
+    <mergeCell ref="A1:I5"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="L2:L4"/>
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:L12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="A11:L11"/>
+    <mergeCell ref="K7:L8"/>
+    <mergeCell ref="A9:B10"/>
+    <mergeCell ref="C9:D10"/>
+    <mergeCell ref="E9:F10"/>
+    <mergeCell ref="G9:H10"/>
+    <mergeCell ref="I9:J10"/>
+    <mergeCell ref="K9:L10"/>
+    <mergeCell ref="A7:B8"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="E7:F8"/>
+    <mergeCell ref="G7:H8"/>
+    <mergeCell ref="I7:J8"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="J19:K19"/>
     <mergeCell ref="A48:L48"/>
     <mergeCell ref="A49:L55"/>
     <mergeCell ref="A31:A38"/>
@@ -2232,53 +2238,41 @@
     <mergeCell ref="B35:B36"/>
     <mergeCell ref="B37:C38"/>
     <mergeCell ref="D37:L38"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="A11:L11"/>
-    <mergeCell ref="K7:L8"/>
-    <mergeCell ref="A9:B10"/>
-    <mergeCell ref="C9:D10"/>
-    <mergeCell ref="E9:F10"/>
-    <mergeCell ref="G9:H10"/>
-    <mergeCell ref="I9:J10"/>
-    <mergeCell ref="K9:L10"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:L12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="A1:I5"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="K2:K4"/>
-    <mergeCell ref="L2:L4"/>
-    <mergeCell ref="A6:L6"/>
-    <mergeCell ref="A7:B8"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="E7:F8"/>
-    <mergeCell ref="G7:H8"/>
-    <mergeCell ref="I7:J8"/>
+    <mergeCell ref="A45:L45"/>
+    <mergeCell ref="A46:B47"/>
+    <mergeCell ref="C46:D47"/>
+    <mergeCell ref="E46:F47"/>
+    <mergeCell ref="G46:H47"/>
+    <mergeCell ref="I46:J47"/>
+    <mergeCell ref="K46:L47"/>
+    <mergeCell ref="A23:A30"/>
+    <mergeCell ref="B23:C24"/>
+    <mergeCell ref="D23:F24"/>
+    <mergeCell ref="G23:I24"/>
+    <mergeCell ref="J23:L24"/>
+    <mergeCell ref="B25:C26"/>
+    <mergeCell ref="D25:F26"/>
+    <mergeCell ref="G25:I26"/>
+    <mergeCell ref="J25:L26"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="B29:C30"/>
+    <mergeCell ref="D29:L30"/>
+    <mergeCell ref="A20:L20"/>
+    <mergeCell ref="A21:C22"/>
+    <mergeCell ref="D21:F22"/>
+    <mergeCell ref="G21:I22"/>
+    <mergeCell ref="J21:L22"/>
+    <mergeCell ref="A42:L42"/>
+    <mergeCell ref="A43:B44"/>
+    <mergeCell ref="C43:D44"/>
+    <mergeCell ref="E43:F44"/>
+    <mergeCell ref="I43:J44"/>
+    <mergeCell ref="K43:L44"/>
+    <mergeCell ref="A39:L39"/>
+    <mergeCell ref="A40:B41"/>
+    <mergeCell ref="C40:D41"/>
+    <mergeCell ref="E40:F41"/>
+    <mergeCell ref="I40:J41"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
